--- a/Safe_Results/SA_Capacity_Costs/SA_Capacity_Costs_HPLB.xlsx
+++ b/Safe_Results/SA_Capacity_Costs/SA_Capacity_Costs_HPLB.xlsx
@@ -626,10 +626,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2896.988</v>
+        <v>2257.806</v>
       </c>
       <c r="G4" t="n">
-        <v>2688.579</v>
+        <v>2049.397</v>
       </c>
       <c r="H4" t="n">
         <v>208.409</v>
@@ -864,10 +864,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2897.878</v>
+        <v>2323.389</v>
       </c>
       <c r="G4" t="n">
-        <v>2520.519</v>
+        <v>1946.03</v>
       </c>
       <c r="H4" t="n">
         <v>377.359</v>
@@ -1102,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2897.878</v>
+        <v>2323.389</v>
       </c>
       <c r="G4" t="n">
-        <v>2520.519</v>
+        <v>1946.03</v>
       </c>
       <c r="H4" t="n">
         <v>377.359</v>
@@ -1340,10 +1340,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2897.878</v>
+        <v>2323.389</v>
       </c>
       <c r="G4" t="n">
-        <v>2520.519</v>
+        <v>1946.03</v>
       </c>
       <c r="H4" t="n">
         <v>377.359</v>
@@ -1578,10 +1578,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2897.878</v>
+        <v>2323.389</v>
       </c>
       <c r="G4" t="n">
-        <v>2520.519</v>
+        <v>1946.03</v>
       </c>
       <c r="H4" t="n">
         <v>377.359</v>
